--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N5_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N5_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>99.53774699466139</v>
+        <v>16.17488388663248</v>
       </c>
       <c r="D2" t="n">
-        <v>60.39632480029488</v>
+        <v>9.814402780047917</v>
       </c>
       <c r="E2" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F2" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>105.4017920921507</v>
+        <v>17.12779121497449</v>
       </c>
       <c r="D3" t="n">
-        <v>65.1922370975086</v>
+        <v>10.59373852834515</v>
       </c>
       <c r="E3" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F3" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>60.03262595658237</v>
+        <v>9.755301717944636</v>
       </c>
       <c r="D4" t="n">
-        <v>38.82426037013986</v>
+        <v>6.308942310147728</v>
       </c>
       <c r="E4" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F4" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>59.26029404907123</v>
+        <v>9.629797782974075</v>
       </c>
       <c r="D5" t="n">
-        <v>30.43846251044885</v>
+        <v>4.946250157947937</v>
       </c>
       <c r="E5" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F5" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>63.9920811177853</v>
+        <v>10.39871318164011</v>
       </c>
       <c r="D6" t="n">
-        <v>27.55449146690971</v>
+        <v>4.477604863372828</v>
       </c>
       <c r="E6" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F6" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>84.89474266884753</v>
+        <v>13.79539568368772</v>
       </c>
       <c r="D7" t="n">
-        <v>78.18532407164767</v>
+        <v>12.70511516164275</v>
       </c>
       <c r="E7" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F7" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>69.56801309591566</v>
+        <v>11.3048021280863</v>
       </c>
       <c r="D8" t="n">
-        <v>62.75357524198108</v>
+        <v>10.19745597682193</v>
       </c>
       <c r="E8" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F8" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>65.75775359655137</v>
+        <v>10.6856349594396</v>
       </c>
       <c r="D9" t="n">
-        <v>25.16445906432324</v>
+        <v>4.089224597952526</v>
       </c>
       <c r="E9" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F9" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>37.19858783075578</v>
+        <v>6.044770522497814</v>
       </c>
       <c r="D10" t="n">
-        <v>21.70829334609241</v>
+        <v>3.527597668740017</v>
       </c>
       <c r="E10" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F10" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>73.44616643956569</v>
+        <v>11.93500204642942</v>
       </c>
       <c r="D11" t="n">
-        <v>27.64300442233232</v>
+        <v>4.491988218629002</v>
       </c>
       <c r="E11" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F11" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>54.94656953419515</v>
+        <v>8.928817549306713</v>
       </c>
       <c r="D12" t="n">
-        <v>8.938685500330905</v>
+        <v>1.452536393803772</v>
       </c>
       <c r="E12" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F12" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>34.55093641837307</v>
+        <v>5.614527167985624</v>
       </c>
       <c r="D13" t="n">
-        <v>7.32663054394678</v>
+        <v>1.190577463391352</v>
       </c>
       <c r="E13" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F13" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>36.29994609499312</v>
+        <v>5.898741240436383</v>
       </c>
       <c r="D14" t="n">
-        <v>29.96792733549967</v>
+        <v>4.869788192018697</v>
       </c>
       <c r="E14" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F14" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>21.21946821987184</v>
+        <v>3.448163585729175</v>
       </c>
       <c r="D15" t="n">
-        <v>19.83053201505194</v>
+        <v>3.22246145244594</v>
       </c>
       <c r="E15" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F15" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>9.788794589424336</v>
+        <v>1.590679120781455</v>
       </c>
       <c r="D16" t="n">
-        <v>10.05368092125313</v>
+        <v>1.633723149703633</v>
       </c>
       <c r="E16" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F16" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>71.04724131078233</v>
+        <v>11.54517671300213</v>
       </c>
       <c r="D17" t="n">
-        <v>66.64451944186519</v>
+        <v>10.82973440930309</v>
       </c>
       <c r="E17" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F17" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>20.13046249379066</v>
+        <v>3.271200155240983</v>
       </c>
       <c r="D18" t="n">
-        <v>24.11031189165685</v>
+        <v>3.917925682394237</v>
       </c>
       <c r="E18" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F18" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>12.25725121483018</v>
+        <v>1.991803322409903</v>
       </c>
       <c r="D19" t="n">
-        <v>16.21710004005098</v>
+        <v>2.635278756508284</v>
       </c>
       <c r="E19" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F19" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>49.83714022026371</v>
+        <v>8.098535285792854</v>
       </c>
       <c r="D20" t="n">
-        <v>5.585233540729352</v>
+        <v>0.9076004503685197</v>
       </c>
       <c r="E20" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F20" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>39.71474424925788</v>
+        <v>6.453645940504407</v>
       </c>
       <c r="D21" t="n">
-        <v>11.63925350794553</v>
+        <v>1.891378695041149</v>
       </c>
       <c r="E21" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F21" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>30.74636845738775</v>
+        <v>4.996284874325509</v>
       </c>
       <c r="D22" t="n">
-        <v>16.43590243609669</v>
+        <v>2.670834145865712</v>
       </c>
       <c r="E22" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F22" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>12.24700517960572</v>
+        <v>1.99013834168593</v>
       </c>
       <c r="D23" t="n">
-        <v>17.72271529433277</v>
+        <v>2.879941235329075</v>
       </c>
       <c r="E23" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F23" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>20.6307183208339</v>
+        <v>3.352491727135509</v>
       </c>
       <c r="D24" t="n">
-        <v>12.32999612092229</v>
+        <v>2.003624369649872</v>
       </c>
       <c r="E24" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F24" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>30.27026523483001</v>
+        <v>4.918918100659877</v>
       </c>
       <c r="D25" t="n">
-        <v>18.29554265917595</v>
+        <v>2.973025682116091</v>
       </c>
       <c r="E25" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F25" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>65.91071486314526</v>
+        <v>10.71049116526111</v>
       </c>
       <c r="D26" t="n">
-        <v>57.45106401136724</v>
+        <v>9.335797901847178</v>
       </c>
       <c r="E26" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F26" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>42.92604340274799</v>
+        <v>6.975482052946549</v>
       </c>
       <c r="D27" t="n">
-        <v>3.180491637322371</v>
+        <v>0.5168298910648853</v>
       </c>
       <c r="E27" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F27" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>11.96083913306936</v>
+        <v>1.943636359123771</v>
       </c>
       <c r="D28" t="n">
-        <v>19.06981037569957</v>
+        <v>3.098844186051181</v>
       </c>
       <c r="E28" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F28" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>15.33999185546442</v>
+        <v>2.492748676512968</v>
       </c>
       <c r="D29" t="n">
-        <v>8.897048807599571</v>
+        <v>1.44577043123493</v>
       </c>
       <c r="E29" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F29" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>30.89537510228739</v>
+        <v>5.020498454121701</v>
       </c>
       <c r="D30" t="n">
-        <v>12.50579770722524</v>
+        <v>2.032192127424102</v>
       </c>
       <c r="E30" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F30" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>32.11386297149666</v>
+        <v>5.218502732868207</v>
       </c>
       <c r="D31" t="n">
-        <v>5.752200665832164</v>
+        <v>0.9347326081977266</v>
       </c>
       <c r="E31" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F31" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>79.92446423011332</v>
+        <v>12.98772543739342</v>
       </c>
       <c r="D32" t="n">
-        <v>66.38202680446921</v>
+        <v>10.78707935572625</v>
       </c>
       <c r="E32" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F32" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>4.536190310481845</v>
+        <v>0.7371309254532998</v>
       </c>
       <c r="D33" t="n">
-        <v>18.41429279741692</v>
+        <v>2.99232257958025</v>
       </c>
       <c r="E33" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F33" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>13.65461926999598</v>
+        <v>2.218875631374348</v>
       </c>
       <c r="D34" t="n">
-        <v>5.471213020591638</v>
+        <v>0.8890721158461412</v>
       </c>
       <c r="E34" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F34" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>11.45068003608282</v>
+        <v>1.860735505863458</v>
       </c>
       <c r="D35" t="n">
-        <v>12.13951151436578</v>
+        <v>1.972670621084439</v>
       </c>
       <c r="E35" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F35" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>10.86109387105936</v>
+        <v>1.764927754047147</v>
       </c>
       <c r="D36" t="n">
-        <v>12.05582657044931</v>
+        <v>1.959071817698012</v>
       </c>
       <c r="E36" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F36" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>44.79036458625237</v>
+        <v>7.27843424526601</v>
       </c>
       <c r="D37" t="n">
-        <v>18.03799403773085</v>
+        <v>2.931174031131264</v>
       </c>
       <c r="E37" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F37" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>27.000754713139</v>
+        <v>4.387622640885088</v>
       </c>
       <c r="D38" t="n">
-        <v>5.811912328124198</v>
+        <v>0.9444357533201823</v>
       </c>
       <c r="E38" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F38" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>24.67851433797216</v>
+        <v>4.010258579920476</v>
       </c>
       <c r="D39" t="n">
-        <v>3.85452646147538</v>
+        <v>0.6263605499897493</v>
       </c>
       <c r="E39" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F39" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1696,16 +1696,16 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>24.90795947961428</v>
+        <v>4.047543415437321</v>
       </c>
       <c r="D40" t="n">
-        <v>2.889610714899018</v>
+        <v>0.4695617411710903</v>
       </c>
       <c r="E40" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F40" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1728,16 +1728,16 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>31.62034300488106</v>
+        <v>5.138305738293172</v>
       </c>
       <c r="D41" t="n">
-        <v>13.62176210781679</v>
+        <v>2.213536342520228</v>
       </c>
       <c r="E41" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F41" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1760,16 +1760,16 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>9.943554831439346</v>
+        <v>1.615827660108894</v>
       </c>
       <c r="D42" t="n">
-        <v>20.035900864661</v>
+        <v>3.255833890507412</v>
       </c>
       <c r="E42" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F42" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1792,16 +1792,16 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>27.72914854466947</v>
+        <v>4.505986638508789</v>
       </c>
       <c r="D43" t="n">
-        <v>27.20804619552418</v>
+        <v>4.421307506772679</v>
       </c>
       <c r="E43" t="n">
-        <v>25.88416591435062</v>
+        <v>4.206176961081975</v>
       </c>
       <c r="F43" t="n">
-        <v>20.24609361458937</v>
+        <v>3.289990212370772</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
